--- a/docs/downloads/Stage 2 - Select.xlsx
+++ b/docs/downloads/Stage 2 - Select.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>6-8 hours per account per quarter across a portfolio of multiple accounts. A CSD managing 10 accounts spends 60-80 hours per quarter on this workflow alone — easily exceeding 10 hrs/month saved. The combination of high per-occurrence cost and quarterly frequency across multiple accounts places this at the top of the anchor scale (Score 5: &gt;10 hrs/month saved).</t>
+          <t>6-8 hours per account per quarter across a portfolio of multiple accounts. A CSM managing 10 accounts spends 60-80 hours per quarter on this workflow alone — easily exceeding 10 hrs/month saved. The combination of high per-occurrence cost and quarterly frequency across multiple accounts places this at the top of the anchor scale (Score 5: &gt;10 hrs/month saved).</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>The health report is an internal deliverable reviewed by the CSD before sharing with anyone — the client never sees the raw agent output. Errors in scoring or narrative are catchable during the internal review step before they cause any damage. No irreversible actions are triggered by the report itself (Score 4: Internal deliverable with a review step; errors are catchable before causing damage).</t>
+          <t>The health report is an internal deliverable reviewed by the CSM before sharing with anyone — the client never sees the raw agent output. Errors in scoring or narrative are catchable during the internal review step before they cause any damage. No irreversible actions are triggered by the report itself (Score 4: Internal deliverable with a review step; errors are catchable before causing damage).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>At 8-12 hours per EBR across a portfolio of accounts, this is one of the highest time-cost workflows on the inventory. During EBR season, a CSD preparing for multiple accounts could spend 30+ hours on EBR prep in a single month. Even averaged across the quarter, the monthly time investment consistently exceeds 10 hours. The per-occurrence cost alone (a full day or more) makes this the joint-most time-intensive workflow alongside the Quarterly Account Health Review (Score 5: &gt;10 hrs/month saved).</t>
+          <t>At 8-12 hours per EBR across a portfolio of accounts, this is one of the highest time-cost workflows on the inventory. During EBR season, a CSM preparing for multiple accounts could spend 30+ hours on EBR prep in a single month. Even averaged across the quarter, the monthly time investment consistently exceeds 10 hours. The per-occurrence cost alone (a full day or more) makes this the joint-most time-intensive workflow alongside the Quarterly Account Health Review (Score 5: &gt;10 hrs/month saved).</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>DISQUALIFIED — Disqualifier 1 applies: The workflow's value comes from the relationship built during the process, not the output. EBR preparation forces the CSD to engage deeply with the account relationship, executive sponsor priorities, and the political dynamics of the client organization. Understanding what story to tell, what to emphasize or downplay, and how the executive audience will receive specific messages IS the relationship work. The preparation process is inseparable from the relationship-building it enables — automating it removes the thing that makes it valuable. Despite scoring 3.25 on the weighted composite, this workflow is removed from ranking entirely.</t>
+          <t>DISQUALIFIED — Disqualifier 1 applies: The workflow's value comes from the relationship built during the process, not the output. EBR preparation forces the CSM to engage deeply with the account relationship, executive sponsor priorities, and the political dynamics of the client organization. Understanding what story to tell, what to emphasize or downplay, and how the executive audience will receive specific messages IS the relationship work. The preparation process is inseparable from the relationship-building it enables — automating it removes the thing that makes it valuable. Despite scoring 3.25 on the weighted composite, this workflow is removed from ranking entirely.</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
